--- a/review/etnografiya/may-december/november/november.xlsx
+++ b/review/etnografiya/may-december/november/november.xlsx
@@ -108,7 +108,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему лаковая коробочка начинается не с дерева?</t>
+          <t xml:space="preserve">Бумага становится прочной федоскинской шкатулкой. Под живописью скрыта работа с основой — привычный материал получает неожиданную долговечную форму.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -135,7 +135,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как глубина появляется на плоской крышке?</t>
+          <t xml:space="preserve">Блеск под федоскинской живописью меняет вид изображения. Свет проходит через художественные слои и становится частью мастерского замысла.</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -162,7 +162,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как разместить несколько эпизодов в ладони?</t>
+          <t xml:space="preserve">На маленькой палехской крышке помещается большой сюжет. Масштаб миниатюры требует точности, чтобы фигуры и события оставались различимыми.</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -189,7 +189,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему похожие коробочки имеют разные авторские почерки?</t>
+          <t xml:space="preserve">Холуйская миниатюра сохраняет почерк местной школы. Общий вид ремесла не стирает различий в том, как мастера строят изображение.</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -216,7 +216,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как окружение помогает прочитать сюжет?</t>
+          <t xml:space="preserve">Мстёрский пейзаж окружает действие миниатюры. Маленькая поверхность вмещает пространство, в котором фигуры получают своё место и направление движения.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -243,7 +243,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему маленькое украшение требует нескольких стадий?</t>
+          <t xml:space="preserve">Цвет ростовской финифти проходит через обжиг. Изображение возникает не одним движением кисти — огонь участвует в работе мастера.</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -270,7 +270,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металл выглядит лёгким кружевом?</t>
+          <t xml:space="preserve">Металлическая нить складывается в ажурную скань. Твёрдый материал выглядит лёгким благодаря изгибам, соединениям и оставленным просветам.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -297,7 +297,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как календарь возвращает семью к ушедшим поколениям?</t>
+          <t xml:space="preserve">Память о родных собирает людей вместе. Обычай Дмитриева дня возвращает внимание к семейной связи, которая продолжается за пределами одной жизни.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему тёмная линия делает узор заметнее?</t>
+          <t xml:space="preserve">Великоустюжская чернь создаёт тёмный рисунок на серебре. Различие поверхностей помогает прочитать тонкую работу на небольшой металлической вещи.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -351,7 +351,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как имя святой входит в мир домашней работы?</t>
+          <t xml:space="preserve">Образ Параскевы Пятницы связан с женскими занятиями в народной традиции. Почитание получает местное выражение в отношении к труду и его ритму.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -378,7 +378,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как металлическая нить держится на ткани?</t>
+          <t xml:space="preserve">Блестящая нить торжокского шитья удерживается на ткани стежками. Под нарядной поверхностью находится точный порядок закрепления материала.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -405,7 +405,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как убрать часть нитей и сохранить ткань?</t>
+          <t xml:space="preserve">В крестецкой строчке часть нитей убирают ради узора. Просветы становятся рисунком, а оставшиеся соединения удерживают ткань целой.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -432,7 +432,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что соединяет крупные элементы узора?</t>
+          <t xml:space="preserve">Мелкая сетка елецкого кружева связывает крупные мотивы. Воздушный рисунок держится на деталях, которые легко пропустить при первом взгляде.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -459,7 +459,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как один день объединяет работу и посиделки?</t>
+          <t xml:space="preserve">Кузьминки соединяют ремесленный труд с молодёжным общением. Праздничный день открывает другой порядок встречи внутри сезона вечерней работы.</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Может ли народное кружево рассказывать о машине?</t>
+          <t xml:space="preserve">Трактор появляется внутри кружевного узора. Народная техника принимает машинный сюжет — традиционное ремесло рассказывает о новой эпохе.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как рисунок рассчитан на ношение?</t>
+          <t xml:space="preserve">Букет павловопосадского платка остаётся виден в складках. Композиция рассчитана на ношение: квадрат ткани работает в объёмном движении.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как материал соединяет лёгкость и укрытие?</t>
+          <t xml:space="preserve">Тонкая пуховая нить собирается в оренбургский платок. Лёгкость вещи связана с материалом и вязанием, которые можно рассмотреть вблизи.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -567,7 +567,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как тяжёлый материал сохраняет тонкие детали?</t>
+          <t xml:space="preserve">Каслинское литьё передаёт тонкие детали в тяжёлом металле. Видимая лёгкость формы требует точной работы на разных этапах изготовления.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что меняется, когда рисунок попадает на тёмную основу?</t>
+          <t xml:space="preserve">Тёмный тагильский поднос становится цветочным полем. Роспись меняет восприятие металла, сохраняя форму вещи для повседневного использования.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как сохранить прочность вокруг тонких отверстий?</t>
+          <t xml:space="preserve">Шемогодский узор прорезан в бересте насквозь. Тонкие перемычки удерживают ажур целым — красота зависит от сохранённой прочности материала.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что здесь сделал мастер, а что выросло само?</t>
+          <t xml:space="preserve">Вятский кап приносит природный рисунок ещё до обработки. Мастер выбирает форму, в которой выросшая структура дерева становится видимой.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как ажурная деталь складывается в цельную вещь?</t>
+          <t xml:space="preserve">Холмогорская резьба складывает ажур из маленьких просветов. Отдельная костяная деталь требует точного соединения с остальными частями вещи.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Можно ли узнать занятие человека по маленькой фигуре?</t>
+          <t xml:space="preserve">Тобольская миниатюра передаёт занятие человека в малом масштабе. Жест и рабочий предмет помогают прочитать сцену без длинного пояснения.</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -729,7 +729,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как округлый рельеф создаёт игру света?</t>
+          <t xml:space="preserve">Листья кудринской резьбы выступают над поверхностью дерева. Округлый рельеф меняет свет и тень, когда взгляд смещается вокруг вещи.</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему рисунок должен учитывать ручку и край?</t>
+          <t xml:space="preserve">Роспись дулёвской чашки учитывает ручку и край. Цветок попадает на предмет, которым пользуются, — художественная композиция встречается с формой посуды.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Где заканчивается ёмкость и начинается фигурный декор?</t>
+          <t xml:space="preserve">Скопинский сосуд соединяет ёмкость с фигурным декором. Среди затейливых деталей остаются горло, ручка и рабочее устройство посуды.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Чем интересен промысел, о котором редко слышат?</t>
+          <t xml:space="preserve">Судогодская игрушка сохраняет местный почерк в маленькой форме. Сравнение близких вещей помогает заметить отличия, которые теряются за общим словом «промысел».</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Как перестать воспринимать промысел как безымянное производство?</t>
+          <t xml:space="preserve">Подпись возвращает узору имя мастера. Народное ремесло состоит из труда конкретных людей — знакомый рисунок не возникает сам по себе.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Что начинающий ещё не умеет делать автоматически?</t>
+          <t xml:space="preserve">Ученическая ошибка показывает ещё не освоенный приём. Сравнение работ делает видимым путь руки от первой попытки к уверенной точности мастера.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Почему вечерний труд легче представить с другими людьми?</t>
+          <t xml:space="preserve">На посиделках трудятся и разговаривают вместе. Вечерняя работа становится местом общения, где передаются песни, рассказы и повседневный опыт.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
